--- a/figures/Figure2/data/computed/H2O_rhyolite_exps_df.xlsx
+++ b/figures/Figure2/data/computed/H2O_rhyolite_exps_df.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="37">
   <si>
     <t>SiO2</t>
   </si>
@@ -49,21 +49,12 @@
     <t>H2O</t>
   </si>
   <si>
-    <t>CO2</t>
-  </si>
-  <si>
     <t>Citation</t>
   </si>
   <si>
-    <t>Rock Type</t>
-  </si>
-  <si>
     <t>Simplified Rock Type</t>
   </si>
   <si>
-    <t>vols</t>
-  </si>
-  <si>
     <t>T_C</t>
   </si>
   <si>
@@ -76,46 +67,46 @@
     <t>Ab</t>
   </si>
   <si>
-    <t>SAT-NZC4-9†</t>
-  </si>
-  <si>
-    <t>SAT-CAM73-6†</t>
+    <t>SAT-NZC4-9</t>
+  </si>
+  <si>
+    <t>SAT-CAM73-6</t>
   </si>
   <si>
     <t>Ab-duplicate-1</t>
   </si>
   <si>
-    <t>Shaw, 2kb\</t>
-  </si>
-  <si>
-    <t>SAT-NZC4-11†</t>
-  </si>
-  <si>
-    <t>SAT-CAM73-7†</t>
-  </si>
-  <si>
-    <t>SAT-NZC4-4*</t>
-  </si>
-  <si>
-    <t>PDIKS111#</t>
-  </si>
-  <si>
-    <t>PDIKS113#</t>
-  </si>
-  <si>
-    <t>Shaw, 1kb\</t>
-  </si>
-  <si>
-    <t>PDIKS115#</t>
+    <t>Shaw, 2kb</t>
+  </si>
+  <si>
+    <t>SAT-NZC4-11</t>
+  </si>
+  <si>
+    <t>SAT-CAM73-7</t>
+  </si>
+  <si>
+    <t>SAT-NZC4-4</t>
+  </si>
+  <si>
+    <t>PDIKS111</t>
+  </si>
+  <si>
+    <t>PDIKS113</t>
+  </si>
+  <si>
+    <t>Shaw, 1kb</t>
+  </si>
+  <si>
+    <t>PDIKS115</t>
   </si>
   <si>
     <t>Ab-duplicate-2</t>
   </si>
   <si>
-    <t>PDIKS102#</t>
-  </si>
-  <si>
-    <t>PDIKS110#</t>
+    <t>PDIKS102</t>
+  </si>
+  <si>
+    <t>PDIKS110</t>
   </si>
   <si>
     <t>Benne and Behrens, 2003</t>
@@ -127,19 +118,10 @@
     <t>Shaw 1963</t>
   </si>
   <si>
-    <t>Moore et al. 1995a</t>
+    <t>Moore et al. 1995</t>
   </si>
   <si>
     <t>Silver et al. 1990</t>
-  </si>
-  <si>
-    <t>haplobasalt</t>
-  </si>
-  <si>
-    <t>TBD</t>
-  </si>
-  <si>
-    <t>haplo</t>
   </si>
   <si>
     <t>rhyolite</t>
@@ -500,10 +482,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T16"/>
+  <dimension ref="A1:Q16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:20">
+    <row r="1" spans="1:17">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -552,19 +534,10 @@
       <c r="Q1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:17">
+      <c r="A2" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:20">
-      <c r="A2" s="1" t="s">
-        <v>19</v>
       </c>
       <c r="B2">
         <v>69.19</v>
@@ -599,34 +572,25 @@
       <c r="L2">
         <v>12.095</v>
       </c>
-      <c r="M2">
-        <v>0</v>
+      <c r="M2" t="s">
+        <v>31</v>
       </c>
       <c r="N2" t="s">
-        <v>34</v>
-      </c>
-      <c r="O2" t="s">
-        <v>39</v>
-      </c>
-      <c r="P2" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>10</v>
-      </c>
-      <c r="R2">
+        <v>36</v>
+      </c>
+      <c r="O2">
         <v>1200</v>
       </c>
-      <c r="S2">
+      <c r="P2">
         <v>5000</v>
       </c>
-      <c r="T2">
+      <c r="Q2">
         <v>30.50027274788455</v>
       </c>
     </row>
-    <row r="3" spans="1:20">
+    <row r="3" spans="1:17">
       <c r="A3" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B3">
         <v>71.8</v>
@@ -661,34 +625,25 @@
       <c r="L3">
         <v>8</v>
       </c>
-      <c r="M3">
-        <v>0</v>
+      <c r="M3" t="s">
+        <v>32</v>
       </c>
       <c r="N3" t="s">
-        <v>35</v>
-      </c>
-      <c r="O3" t="s">
-        <v>40</v>
-      </c>
-      <c r="P3" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>10</v>
-      </c>
-      <c r="R3">
+        <v>36</v>
+      </c>
+      <c r="O3">
         <v>900</v>
       </c>
-      <c r="S3">
+      <c r="P3">
         <v>2841</v>
       </c>
-      <c r="T3">
+      <c r="Q3">
         <v>22.72240833360146</v>
       </c>
     </row>
-    <row r="4" spans="1:20">
+    <row r="4" spans="1:17">
       <c r="A4" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B4">
         <v>75</v>
@@ -723,34 +678,25 @@
       <c r="L4">
         <v>8.359999999999999</v>
       </c>
-      <c r="M4">
-        <v>0</v>
+      <c r="M4" t="s">
+        <v>32</v>
       </c>
       <c r="N4" t="s">
-        <v>35</v>
-      </c>
-      <c r="O4" t="s">
-        <v>40</v>
-      </c>
-      <c r="P4" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>10</v>
-      </c>
-      <c r="R4">
+        <v>36</v>
+      </c>
+      <c r="O4">
         <v>900</v>
       </c>
-      <c r="S4">
+      <c r="P4">
         <v>2827</v>
       </c>
-      <c r="T4">
+      <c r="Q4">
         <v>23.50001470322588</v>
       </c>
     </row>
-    <row r="5" spans="1:20">
+    <row r="5" spans="1:17">
       <c r="A5" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B5">
         <v>69.19</v>
@@ -785,34 +731,25 @@
       <c r="L5">
         <v>5.86</v>
       </c>
-      <c r="M5">
-        <v>0</v>
+      <c r="M5" t="s">
+        <v>31</v>
       </c>
       <c r="N5" t="s">
-        <v>34</v>
-      </c>
-      <c r="O5" t="s">
-        <v>41</v>
-      </c>
-      <c r="P5" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>10</v>
-      </c>
-      <c r="R5">
+        <v>36</v>
+      </c>
+      <c r="O5">
         <v>1200</v>
       </c>
-      <c r="S5">
+      <c r="P5">
         <v>2000</v>
       </c>
-      <c r="T5">
+      <c r="Q5">
         <v>17.53420954265666</v>
       </c>
     </row>
-    <row r="6" spans="1:20">
+    <row r="6" spans="1:17">
       <c r="A6" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B6">
         <v>76.59999999999999</v>
@@ -847,34 +784,25 @@
       <c r="L6">
         <v>6.2</v>
       </c>
-      <c r="M6">
-        <v>0</v>
+      <c r="M6" t="s">
+        <v>33</v>
       </c>
       <c r="N6" t="s">
         <v>36</v>
       </c>
-      <c r="O6" t="s">
-        <v>40</v>
-      </c>
-      <c r="P6" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>10</v>
-      </c>
-      <c r="R6">
+      <c r="O6">
         <v>800</v>
       </c>
-      <c r="S6">
+      <c r="P6">
         <v>2000</v>
       </c>
-      <c r="T6">
+      <c r="Q6">
         <v>18.29296450310542</v>
       </c>
     </row>
-    <row r="7" spans="1:20">
+    <row r="7" spans="1:17">
       <c r="A7" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B7">
         <v>71.8</v>
@@ -909,34 +837,25 @@
       <c r="L7">
         <v>6.34</v>
       </c>
-      <c r="M7">
-        <v>0</v>
+      <c r="M7" t="s">
+        <v>32</v>
       </c>
       <c r="N7" t="s">
-        <v>35</v>
-      </c>
-      <c r="O7" t="s">
-        <v>40</v>
-      </c>
-      <c r="P7" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>10</v>
-      </c>
-      <c r="R7">
+        <v>36</v>
+      </c>
+      <c r="O7">
         <v>900</v>
       </c>
-      <c r="S7">
+      <c r="P7">
         <v>1986</v>
       </c>
-      <c r="T7">
+      <c r="Q7">
         <v>18.89855659825731</v>
       </c>
     </row>
-    <row r="8" spans="1:20">
+    <row r="8" spans="1:17">
       <c r="A8" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B8">
         <v>75</v>
@@ -971,34 +890,25 @@
       <c r="L8">
         <v>6.34</v>
       </c>
-      <c r="M8">
-        <v>0</v>
+      <c r="M8" t="s">
+        <v>32</v>
       </c>
       <c r="N8" t="s">
-        <v>35</v>
-      </c>
-      <c r="O8" t="s">
-        <v>40</v>
-      </c>
-      <c r="P8" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>10</v>
-      </c>
-      <c r="R8">
+        <v>36</v>
+      </c>
+      <c r="O8">
         <v>900</v>
       </c>
-      <c r="S8">
+      <c r="P8">
         <v>1848</v>
       </c>
-      <c r="T8">
+      <c r="Q8">
         <v>18.89466460759451</v>
       </c>
     </row>
-    <row r="9" spans="1:20">
+    <row r="9" spans="1:17">
       <c r="A9" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B9">
         <v>71.8</v>
@@ -1033,34 +943,25 @@
       <c r="L9">
         <v>5.23</v>
       </c>
-      <c r="M9">
-        <v>0</v>
+      <c r="M9" t="s">
+        <v>34</v>
       </c>
       <c r="N9" t="s">
-        <v>37</v>
-      </c>
-      <c r="O9" t="s">
-        <v>40</v>
-      </c>
-      <c r="P9" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>10</v>
-      </c>
-      <c r="R9">
+        <v>36</v>
+      </c>
+      <c r="O9">
         <v>1000</v>
       </c>
-      <c r="S9">
+      <c r="P9">
         <v>1470</v>
       </c>
-      <c r="T9">
+      <c r="Q9">
         <v>16.12329637733639</v>
       </c>
     </row>
-    <row r="10" spans="1:20">
+    <row r="10" spans="1:17">
       <c r="A10" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B10">
         <v>77.5</v>
@@ -1095,34 +996,25 @@
       <c r="L10">
         <v>5.06</v>
       </c>
-      <c r="M10">
-        <v>0</v>
+      <c r="M10" t="s">
+        <v>35</v>
       </c>
       <c r="N10" t="s">
-        <v>38</v>
-      </c>
-      <c r="O10" t="s">
-        <v>40</v>
-      </c>
-      <c r="P10" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>10</v>
-      </c>
-      <c r="R10">
+        <v>36</v>
+      </c>
+      <c r="O10">
         <v>850</v>
       </c>
-      <c r="S10">
+      <c r="P10">
         <v>1470</v>
       </c>
-      <c r="T10">
+      <c r="Q10">
         <v>15.38494602593619</v>
       </c>
     </row>
-    <row r="11" spans="1:20">
+    <row r="11" spans="1:17">
       <c r="A11" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B11">
         <v>77.5</v>
@@ -1157,34 +1049,25 @@
       <c r="L11">
         <v>4.43</v>
       </c>
-      <c r="M11">
-        <v>0</v>
+      <c r="M11" t="s">
+        <v>35</v>
       </c>
       <c r="N11" t="s">
-        <v>38</v>
-      </c>
-      <c r="O11" t="s">
-        <v>40</v>
-      </c>
-      <c r="P11" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>10</v>
-      </c>
-      <c r="R11">
+        <v>36</v>
+      </c>
+      <c r="O11">
         <v>850</v>
       </c>
-      <c r="S11">
+      <c r="P11">
         <v>1260</v>
       </c>
-      <c r="T11">
+      <c r="Q11">
         <v>13.73247696067277</v>
       </c>
     </row>
-    <row r="12" spans="1:20">
+    <row r="12" spans="1:17">
       <c r="A12" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B12">
         <v>76.59999999999999</v>
@@ -1219,34 +1102,25 @@
       <c r="L12">
         <v>4.3</v>
       </c>
-      <c r="M12">
-        <v>0</v>
+      <c r="M12" t="s">
+        <v>33</v>
       </c>
       <c r="N12" t="s">
         <v>36</v>
       </c>
-      <c r="O12" t="s">
-        <v>40</v>
-      </c>
-      <c r="P12" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>10</v>
-      </c>
-      <c r="R12">
+      <c r="O12">
         <v>900</v>
       </c>
-      <c r="S12">
+      <c r="P12">
         <v>1000</v>
       </c>
-      <c r="T12">
+      <c r="Q12">
         <v>13.44051923337117</v>
       </c>
     </row>
-    <row r="13" spans="1:20">
+    <row r="13" spans="1:17">
       <c r="A13" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B13">
         <v>77.5</v>
@@ -1281,34 +1155,25 @@
       <c r="L13">
         <v>3.94</v>
       </c>
-      <c r="M13">
-        <v>0</v>
+      <c r="M13" t="s">
+        <v>35</v>
       </c>
       <c r="N13" t="s">
-        <v>38</v>
-      </c>
-      <c r="O13" t="s">
-        <v>40</v>
-      </c>
-      <c r="P13" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>10</v>
-      </c>
-      <c r="R13">
+        <v>36</v>
+      </c>
+      <c r="O13">
         <v>850</v>
       </c>
-      <c r="S13">
+      <c r="P13">
         <v>980</v>
       </c>
-      <c r="T13">
+      <c r="Q13">
         <v>12.40191269269118</v>
       </c>
     </row>
-    <row r="14" spans="1:20">
+    <row r="14" spans="1:17">
       <c r="A14" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B14">
         <v>69.19</v>
@@ -1343,34 +1208,25 @@
       <c r="L14">
         <v>2.565</v>
       </c>
-      <c r="M14">
-        <v>0</v>
+      <c r="M14" t="s">
+        <v>31</v>
       </c>
       <c r="N14" t="s">
-        <v>34</v>
-      </c>
-      <c r="O14" t="s">
-        <v>41</v>
-      </c>
-      <c r="P14" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>10</v>
-      </c>
-      <c r="R14">
+        <v>36</v>
+      </c>
+      <c r="O14">
         <v>1200</v>
       </c>
-      <c r="S14">
+      <c r="P14">
         <v>500</v>
       </c>
-      <c r="T14">
+      <c r="Q14">
         <v>8.514414548033461</v>
       </c>
     </row>
-    <row r="15" spans="1:20">
+    <row r="15" spans="1:17">
       <c r="A15" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B15">
         <v>77.5</v>
@@ -1405,34 +1261,25 @@
       <c r="L15">
         <v>3.15</v>
       </c>
-      <c r="M15">
-        <v>0</v>
+      <c r="M15" t="s">
+        <v>35</v>
       </c>
       <c r="N15" t="s">
-        <v>38</v>
-      </c>
-      <c r="O15" t="s">
-        <v>40</v>
-      </c>
-      <c r="P15" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>10</v>
-      </c>
-      <c r="R15">
+        <v>36</v>
+      </c>
+      <c r="O15">
         <v>850</v>
       </c>
-      <c r="S15">
+      <c r="P15">
         <v>500</v>
       </c>
-      <c r="T15">
+      <c r="Q15">
         <v>10.16808222310751</v>
       </c>
     </row>
-    <row r="16" spans="1:20">
+    <row r="16" spans="1:17">
       <c r="A16" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B16">
         <v>77.5</v>
@@ -1467,28 +1314,19 @@
       <c r="L16">
         <v>1.46</v>
       </c>
-      <c r="M16">
-        <v>0</v>
+      <c r="M16" t="s">
+        <v>35</v>
       </c>
       <c r="N16" t="s">
-        <v>38</v>
-      </c>
-      <c r="O16" t="s">
-        <v>40</v>
-      </c>
-      <c r="P16" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>10</v>
-      </c>
-      <c r="R16">
+        <v>36</v>
+      </c>
+      <c r="O16">
         <v>850</v>
       </c>
-      <c r="S16">
+      <c r="P16">
         <v>190</v>
       </c>
-      <c r="T16">
+      <c r="Q16">
         <v>4.984756690239123</v>
       </c>
     </row>
